--- a/CBT_2022_3회/산업안전기사_2022_3회_문항등록.xlsx
+++ b/CBT_2022_3회/산업안전기사_2022_3회_문항등록.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="문항등록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="사용가이드" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="커리큘럼ID" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="색상범례" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1602,7 +1602,7 @@
       </c>
       <c r="AI4" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;의식수준의 단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;의식수준은 낮아도 위험하고 지나쳐도 위험&lt;/strong&gt; 하다 — &lt;strong&gt;phase Ⅲ(주의 집중)이 가장 좋고 phase Ⅳ(과잉)에서는 하나만 보인다&lt;/strong&gt;. &lt;strong&gt;「돌발」 · 「순간적」이라는 낱말이 과잉&lt;/strong&gt;을 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;돌발사태의 긴장은 의식의 과잉&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;의식수준의 단계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;의식수준은 낮아도 위험하고 지나쳐도 위험&lt;/strong&gt;하다 — &lt;strong&gt;phase Ⅲ(주의 집중)이 가장 좋고 phase Ⅳ(과잉)에서는 하나만 보인다&lt;/strong&gt;. &lt;strong&gt;「돌발」 · 「순간적」이라는 낱말이 과잉&lt;/strong&gt;을 가리킨다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;돌발사태의 긴장은 의식의 과잉&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2092,17 +2092,17 @@
       </c>
       <c r="AG8" s="32" t="inlineStr">
         <is>
-          <t>넷은 &lt;strong&gt;Man · Machine · Media · Management&lt;/strong&gt;다. &lt;strong&gt;Mechanism 이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해의 4M&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;M&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Man(사람)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본인 말고 주위 사람과의 관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심리적 · 생리적 · 직장적 원인&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Machine(기계·설비)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기계와 설비의 결함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「Mechanism」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Media(작업매체)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업정보 · 작업방법 · 작업환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Management(관리)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전관리 조직 · 규정 · 교육 · 점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>넷은 &lt;strong&gt;Man · Machine · Media · Management&lt;/strong&gt;다. &lt;strong&gt;Mechanism이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;재해의 4M&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;M&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;무엇&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Man(사람)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;본인 말고 주위 사람과의 관계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;심리적 · 생리적 · 직장적 원인&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Machine(기계·설비)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;기계와 설비의 결함&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「Mechanism」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Media(작업매체)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작업정보 · 작업방법 · 작업환경&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;Management(관리)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전관리 조직 · 규정 · 교육 · 점검&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH8" s="32" t="inlineStr">
         <is>
-          <t>① Man 은 4M 의 하나다.&lt;br&gt;③ Media 도 그렇다.&lt;br&gt;④ Management 도 그렇다.</t>
+          <t>① Man은 4M의 하나다.&lt;br&gt;③ Media 도 그렇다.&lt;br&gt;④ Management 도 그렇다.</t>
         </is>
       </c>
       <c r="AI8" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;재해원인의 4M&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「사람 · 기계 · 매체 · 관리」&lt;/strong&gt; 네 낱말이다 — &lt;strong&gt;Machine 을 Mechanism 으로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다. &lt;strong&gt;5M 이라 하면 Mission(목적)을 더한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Man · Machine · Media · Management&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;재해원인의 4M&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「사람 · 기계 · 매체 · 관리」&lt;/strong&gt; 네 낱말이다 — &lt;strong&gt;Machine을 Mechanism으로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다. &lt;strong&gt;5M이라 하면 Mission(목적)을 더한다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Man · Machine · Media · Management&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -2995,17 +2995,17 @@
       </c>
       <c r="AG15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;직장 실정에 맞는 구체적·실제적 지도&lt;/strong&gt;가 OJT 의 장점이다. 나머지 셋은 &lt;strong&gt;Off JT&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT 와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가·전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적 · 전문가 · 다른 직장과의 교류 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;직장 실정에 맞는 구체적·실제적 지도&lt;/strong&gt;가 OJT의 장점이다. 나머지 셋은 &lt;strong&gt;Off JT&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;OJT와 Off JT&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;OJT&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;Off JT&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;어디서&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;일하는 자리에서&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;따로 자리를 마련해&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;누가&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;직속상사가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;외부 전문가·전문 강사가&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;몇 명&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;한 사람 또는 소수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여럿을 한꺼번에&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;장점&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;현장 실정에 맞다 · 개별 지도 · 상호 신뢰&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;조직적 · 전문가 · 다른 직장과의 교류 · 여러 매체&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH15" s="32" t="inlineStr">
         <is>
-          <t>② 다른 직장 근로자와 교류할 수 있는 것은 Off JT 의 장점이다.&lt;br&gt;③ 외부 전문가를 위촉하는 것도 그렇다.&lt;br&gt;④ 다수에게 조직적 훈련이 가능한 것도 그렇다.</t>
+          <t>② 다른 직장 근로자와 교류할 수 있는 것은 Off JT의 장점이다.&lt;br&gt;③ 외부 전문가를 위촉하는 것도 그렇다.&lt;br&gt;④ 다수에게 조직적 훈련이 가능한 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI15" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;OJT 와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「우리 현장 · 우리 상사 · 나 한 사람」이면 OJT&lt;/strong&gt;다 — &lt;strong&gt;「다른 직장 · 외부 · 다수」라는 낱말이 하나라도 붙으면 Off JT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현장 실정에 맞으면 OJT&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;OJT와 Off JT&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「우리 현장 · 우리 상사 · 나 한 사람」이면 OJT&lt;/strong&gt;다 — &lt;strong&gt;「다른 직장 · 외부 · 다수」라는 낱말이 하나라도 붙으면 Off JT&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;현장 실정에 맞으면 OJT&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="AG16" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;산업용 원심기&lt;/strong&gt;가 안전검사 대상이다. 나머지 셋은 &lt;strong&gt;모두 제외&lt;/strong&gt; 되는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사 대상 유해·위험 기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인(정격하중 2톤 미만은 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;리프트 · 곤돌라 · 고소작업대(화물자동차·특수자동차 탑재형)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소배기장치(이동식은 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원심기(산업용만)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④ — 이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;롤러기(밀폐형 구조는 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사출성형기(형 체결력 294 [kN] 미만은 제외) · 컨베이어 · 산업용 로봇 · 혼합기 · 파쇄기·분쇄기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;산업용 원심기&lt;/strong&gt;가 안전검사 대상이다. 나머지 셋은 &lt;strong&gt;모두 제외&lt;/strong&gt;되는 것이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사 대상 유해·위험 기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;크레인(정격하중 2톤 미만은 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①은 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;리프트 · 곤돌라 · 고소작업대(화물자동차·특수자동차 탑재형)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소배기장치(이동식은 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②는 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원심기(산업용만)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④ — 이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;롤러기(밀폐형 구조는 제외)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③은 제외 대상&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사출성형기(형 체결력 294 [kN] 미만은 제외) · 컨베이어 · 산업용 로봇 · 혼합기 · 파쇄기·분쇄기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH16" s="32" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="AG18" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;아크용접기&lt;/strong&gt;는 안전검사 대상이 아니다. &lt;strong&gt;자동전격방지기가 자율안전확인대상 방호장치&lt;/strong&gt; 일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사 대상 유해·위험 기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기 · 크레인 · 리프트 · 곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소배기장치 · 원심기 · 롤러기 · 사출성형기 · 고소작업대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;컨베이어 · 산업용 로봇 · 혼합기 · 파쇄기·분쇄기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아크용접기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전검사 대상이 아니다&lt;/u&gt; — 자동전격방지기가 자율안전확인대상 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;아크용접기&lt;/strong&gt;는 안전검사 대상이 아니다. &lt;strong&gt;자동전격방지기가 자율안전확인대상 방호장치&lt;/strong&gt;일 뿐이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전검사 대상 유해·위험 기계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대상&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;프레스 · 전단기 · 압력용기 · 크레인 · 리프트 · 곤돌라&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;국소배기장치 · 원심기 · 롤러기 · 사출성형기 · 고소작업대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;컨베이어 · 산업용 로봇 · 혼합기 · 파쇄기·분쇄기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;아크용접기&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전검사 대상이 아니다&lt;/u&gt; — 자동전격방지기가 자율안전확인대상 방호장치&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH18" s="32" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="AG19" s="32" t="inlineStr">
         <is>
-          <t>휴업일수는 연근로일수를 곱해 환산한다. $120 + 73 \times \dfrac{270}{365} = 120 + 54 = 174$ 일이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근로손실일수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120일 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휴업일수 환산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$73 \times \dfrac{270}{365} = 54$ 일&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연근로일수/365 를 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 + 54 = 174일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망·장해가 있으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급별 근로손실일수를 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사망 7,500일&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>휴업일수는 연근로일수를 곱해 환산한다. $120 + 73 \times \dfrac{270}{365} = 120 + 54 = 174$ 일이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근로손실일수의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;근로손실일수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120일 그대로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;휴업일수 환산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$73 \times \dfrac{270}{365} = 54$일&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;연근로일수/365를 곱한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;합계&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;120 + 54 = 174일&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;사망·장해가 있으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;신체장해등급별 근로손실일수를 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;사망 7,500일&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH19" s="32" t="inlineStr">
@@ -3521,7 +3521,7 @@
       </c>
       <c r="AI19" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;근로손실일수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;휴업일수는 「달력의 날」이고 근로손실일수는 「일하는 날」&lt;/strong&gt;이라 &lt;strong&gt;연근로일수/365 를 곱해 바꿔&lt;/strong&gt; 준다. &lt;strong&gt;그대로 더하면 193 이 나와 ④로 끌린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수 × 연근로일수/365&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;근로손실일수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;휴업일수는 「달력의 날」이고 근로손실일수는 「일하는 날」&lt;/strong&gt;이라 &lt;strong&gt;연근로일수/365를 곱해 바꿔&lt;/strong&gt; 준다. &lt;strong&gt;그대로 더하면 193이 나와 ④로 끌린다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;휴업일수 × 연근로일수/365&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4161,7 +4161,7 @@
       </c>
       <c r="AH24" s="32" t="inlineStr">
         <is>
-          <t>① human factors 는 인간공학을 가리킨다.&lt;br&gt;② ergonomics 도 그렇다.&lt;br&gt;③ human engineering 도 그렇다.</t>
+          <t>① human factors는 인간공학을 가리킨다.&lt;br&gt;② ergonomics 도 그렇다.&lt;br&gt;③ human engineering 도 그렇다.</t>
         </is>
       </c>
       <c r="AI24" s="32" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="AH25" s="32" t="inlineStr">
         <is>
-          <t>① critical set 은 FTA 에서 쓰는 용어가 아니다.&lt;br&gt;② 「minimal gate」라는 말도 없다.&lt;br&gt;④ Boolean indicated cut set 은 불 대수로 나타낸 컷셋을 가리킨다.</t>
+          <t>① critical set은 FTA에서 쓰는 용어가 아니다.&lt;br&gt;② 「minimal gate」라는 말도 없다.&lt;br&gt;④ Boolean indicated cut set은 불 대수로 나타낸 컷셋을 가리킨다.</t>
         </is>
       </c>
       <c r="AI25" s="32" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="AG26" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;손바닥 → 손가락 → 손가락 끝&lt;/strong&gt; 순으로 작아진다. &lt;strong&gt;값이 작을수록 예민&lt;/strong&gt; 하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;2점 문턱값(two-point threshold)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 점을 두 점으로 느낄 수 있는 가장 짧은 거리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;값이 작으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그만큼 예민하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예민한 차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손가락 끝 &amp;gt; 손가락 &amp;gt; 손바닥&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;문턱값이 줄어드는 차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손바닥 → 손가락 → 손가락 끝&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가장 둔한 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등 · 넓적다리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;손바닥 → 손가락 → 손가락 끝&lt;/strong&gt; 순으로 작아진다. &lt;strong&gt;값이 작을수록 예민&lt;/strong&gt;하다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;2점 문턱값(two-point threshold)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;무엇&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 점을 두 점으로 느낄 수 있는 가장 짧은 거리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;값이 작으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;그만큼 예민하다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;예민한 차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손가락 끝 &amp;gt; 손가락 &amp;gt; 손바닥&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;문턱값이 줄어드는 차례&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;손바닥 → 손가락 → 손가락 끝&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;가장 둔한 곳&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;등 · 넓적다리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH26" s="32" t="inlineStr">
@@ -4527,17 +4527,17 @@
       </c>
       <c r="AG27" s="32" t="inlineStr">
         <is>
-          <t>$0.09 + 0.05 + 0.26 + 0.04 + 0.04 = 0.48$ [clo] 다. &lt;strong&gt;그대로 더한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보온율(clo)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 clo&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [℃], 상대습도 50%, 기류 0.5 [m/s] 에서 앉아 쉴 때 편안한 옷의 보온력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총보온율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입은 옷의 clo 값을 그대로 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 clo 의 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.155 [ m^{2} \cdot {}^{\circ}\mathrm{C} / W ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 clo&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$0.09 + 0.05 + 0.26 + 0.04 + 0.04 = 0.48$ [clo]다. &lt;strong&gt;그대로 더한다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;보온율(clo)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 clo&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;21 [℃], 상대습도 50%, 기류 0.5 [m/s]에서 앉아 쉴 때 편안한 옷의 보온력&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총보온율&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;입은 옷의 clo 값을 그대로 더한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1 clo의 값&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$0.155 [ m^{2} \cdot {}^{\circ}\mathrm{C} / W ]$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0 clo&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH27" s="32" t="inlineStr">
         <is>
-          <t>① 0.260 은 바지 하나의 값이다.&lt;br&gt;③ 1.184 는 계산과 맞지 않는다.&lt;br&gt;④ 1.280 도 그렇다.</t>
+          <t>① 0.260은 바지 하나의 값이다.&lt;br&gt;③ 1.184는 계산과 맞지 않는다.&lt;br&gt;④ 1.280 도 그렇다.</t>
         </is>
       </c>
       <c r="AI27" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;보온율(clo)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;clo 는 「겹쳐 입으면 더해진다」&lt;/strong&gt;는 단순한 값이다 — &lt;strong&gt;셈이 아니라 덧셈이 전부&lt;/strong&gt;다. &lt;strong&gt;1 clo 가 「봄가을 실내복 한 벌」&lt;/strong&gt; 쯤이라고 새겨 두면 0.48 이 얇은 차림임을 알 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;clo 는 그대로 더한다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;보온율(clo)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;clo는 「겹쳐 입으면 더해진다」&lt;/strong&gt;는 단순한 값이다 — &lt;strong&gt;셈이 아니라 덧셈이 전부&lt;/strong&gt;다. &lt;strong&gt;1 clo가 「봄가을 실내복 한 벌」&lt;/strong&gt; 쯤이라고 새겨 두면 0.48이 얇은 차림임을 알 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;clo는 그대로 더한다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4777,17 +4777,17 @@
       </c>
       <c r="AG29" s="32" t="inlineStr">
         <is>
-          <t>넷은 &lt;strong&gt;Eliminate · Combine · Rearrange · Simplify&lt;/strong&gt;다. &lt;strong&gt;S 는 Safety 가 아니라 Simplify&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;개선의 ECRS 원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Eliminate(제거)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 일을 없앨 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Combine(결합)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 일과 합칠 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Rearrange(재조정)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;차례를 바꿀 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Simplify(단순화)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 간단히 할 수 없나&lt;/u&gt; — 「Safety」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>넷은 &lt;strong&gt;Eliminate · Combine · Rearrange · Simplify&lt;/strong&gt;다. &lt;strong&gt;S는 Safety가 아니라 Simplify&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;개선의 ECRS 원칙&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;E&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Eliminate(제거)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;이 일을 없앨 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;C&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Combine(결합)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;다른 일과 합칠 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Rearrange(재조정)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;차례를 바꿀 수 없나&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;S&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Simplify(단순화)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;더 간단히 할 수 없나&lt;/u&gt; — 「Safety」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH29" s="32" t="inlineStr">
         <is>
-          <t>① 제거는 ECRS 의 E 다.&lt;br&gt;② 결합은 C 다.&lt;br&gt;③ 재조정은 R 다.</t>
+          <t>① 제거는 ECRS의 E다.&lt;br&gt;② 결합은 C다.&lt;br&gt;③ 재조정은 R다.</t>
         </is>
       </c>
       <c r="AI29" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업개선의 ECRS&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 물음이 「없앨까 · 합칠까 · 바꿀까 · 줄일까」&lt;/strong&gt;다 — &lt;strong&gt;앞에서부터 효과가 크다&lt;/strong&gt;. &lt;strong&gt;S 를 Safety 로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;S 는 Simplify&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;작업개선의 ECRS&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;네 물음이 「없앨까 · 합칠까 · 바꿀까 · 줄일까」&lt;/strong&gt;다 — &lt;strong&gt;앞에서부터 효과가 크다&lt;/strong&gt;. &lt;strong&gt;S를 Safety로 바꿔 놓는 것&lt;/strong&gt;이 이 유형의 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;S는 Simplify&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -4910,7 +4910,7 @@
       </c>
       <c r="AG30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;㉡ 이 틀렸다&lt;/strong&gt; — THERP 는 &lt;strong&gt;정성적이 아니라 정량적&lt;/strong&gt;으로 평가한다. 따라서 &lt;strong&gt;㉠ 과 ㉢&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;THERP 의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉠ 인간-기계 계에서 인간의 에러와 그로 인한 위험성을 예측하고 개선한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옳다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉡ 인간의 과오를 정성적으로 평가한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;틀리다&lt;/u&gt; — 정량적으로 평가한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉢ 가지처럼 갈라지는 논리구조와 나무형태의 그래프를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옳다&lt;/u&gt; — 사건나무(event tree)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Technique for Human Error Rate Prediction&lt;/u&gt; — 「Rate(율)」가 정량적임을 말한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;㉡ 이 틀렸다&lt;/strong&gt; — THERP는 &lt;strong&gt;정성적이 아니라 정량적&lt;/strong&gt;으로 평가한다. 따라서 &lt;strong&gt;㉠ 과 ㉢&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;THERP의 특징&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉠ 인간-기계 계에서 인간의 에러와 그로 인한 위험성을 예측하고 개선한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옳다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉡ 인간의 과오를 정성적으로 평가한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;틀리다&lt;/u&gt; — 정량적으로 평가한다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;㉢ 가지처럼 갈라지는 논리구조와 나무형태의 그래프를 쓴다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;옳다&lt;/u&gt; — 사건나무(event tree)&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;Technique for Human Error Rate Prediction&lt;/u&gt; — 「Rate(율)」가 정량적임을 말한다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH30" s="32" t="inlineStr">
@@ -4920,7 +4920,7 @@
       </c>
       <c r="AI30" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;THERP(인간 오류율 예측기법)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;이름 안의 「Rate(율)」&lt;/strong&gt; 하나로 정량적임을 알 수 있다 — &lt;strong&gt;㉡ 의 「정성적」이 곧 오류&lt;/strong&gt;다. &lt;strong&gt;사건나무로 갈래를 치며 확률을 곱해 나간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;THERP 는 정량적&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;THERP(인간 오류율 예측기법)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;이름 안의 「Rate(율)」&lt;/strong&gt; 하나로 정량적임을 알 수 있다 — &lt;strong&gt;㉡ 의 「정성적」이 곧 오류&lt;/strong&gt;다. &lt;strong&gt;사건나무로 갈래를 치며 확률을 곱해 나간다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;THERP는 정량적&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5044,12 +5044,12 @@
       </c>
       <c r="AH31" s="32" t="inlineStr">
         <is>
-          <t>① FHA 는 분담 제작한 부분의 결함을 보는 기법이다.&lt;br&gt;② SHA 는 서브시스템 사이의 위험을 보는 기법이다.&lt;br&gt;④ OHA 는 운용단계의 위험을 보는 기법이다.</t>
+          <t>① FHA는 분담 제작한 부분의 결함을 보는 기법이다.&lt;br&gt;② SHA는 서브시스템 사이의 위험을 보는 기법이다.&lt;br&gt;④ OHA는 운용단계의 위험을 보는 기법이다.</t>
         </is>
       </c>
       <c r="AI31" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「제일 첫 번째 단계」&lt;/strong&gt;라는 말이 그대로 Preliminary 다. &lt;strong&gt;위험수준을 네 등급(파국적 · 위기적 · 한계적 · 무시가능)&lt;/strong&gt;으로 나눈다는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;첫 단계 분석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;예비위험분석(PHA)&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「제일 첫 번째 단계」&lt;/strong&gt;라는 말이 그대로 Preliminary다. &lt;strong&gt;위험수준을 네 등급(파국적 · 위기적 · 한계적 · 무시가능)&lt;/strong&gt;으로 나눈다는 것도 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;첫 단계 분석은 PHA&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5172,12 +5172,12 @@
       </c>
       <c r="AG32" s="32" t="inlineStr">
         <is>
-          <t>병렬부는 $1 - ( 1 - R )^{2} = 2 R - R^{2}$ 다. 전체는 $R \times ( 2 R - R^{2} ) \times R = 2 R^{3} - R^{4}$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직렬과 병렬의 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = R_{1} \times R_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 살아 있어야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나만 살아 있으면 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬부(R ‖ R)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - R )^{2} = 2 R - R^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R \cdot ( 2 R - R^{2} ) \cdot R = 2 R^{3} - R^{4}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>병렬부는 $1 - ( 1 - R )^{2} = 2 R - R^{2}$다. 전체는 $R \times ( 2 R - R^{2} ) \times R = 2 R^{3} - R^{4}$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;직렬과 병렬의 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = R_{1} \times R_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;모두 살아 있어야 한다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} ) \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하나만 살아 있으면 된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬부(R ‖ R)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - ( 1 - R )^{2} = 2 R - R^{2}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전체&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R \cdot ( 2 R - R^{2} ) \cdot R = 2 R^{3} - R^{4}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH32" s="32" t="inlineStr">
         <is>
-          <t>① $R^{4}$ 는 넷을 모두 직렬로 본 값이다.&lt;br&gt;② $2 R - R^{2}$ 는 병렬부만의 신뢰도다.&lt;br&gt;③ $2 R^{2} - R^{3}$ 는 직렬 부품을 하나만 센 값이다.</t>
+          <t>① $R^{4}$는 넷을 모두 직렬로 본 값이다.&lt;br&gt;② $2 R - R^{2}$는 병렬부만의 신뢰도다.&lt;br&gt;③ $2 R^{2} - R^{3}$는 직렬 부품을 하나만 센 값이다.</t>
         </is>
       </c>
       <c r="AI32" s="32" t="inlineStr">
@@ -5301,17 +5301,17 @@
       </c>
       <c r="AG33" s="32" t="inlineStr">
         <is>
-          <t>신뢰도는 $R ( t ) = e^{-\lambda t} = e^{-0.004}$ 이므로 고장확률은 $1 - e^{-0.004}$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지수분포의 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신뢰도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R ( t ) = e^{-\lambda t}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장률이 일정할 때&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장확률(불신뢰도)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$F ( t ) = 1 - e^{-\lambda t}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\lambda t$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.0004 × 10 = 0.004&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTBF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1}{\lambda} = 2 {,} 500$ 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>신뢰도는 $R ( t ) = e^{-\lambda t} = e^{-0.004}$이므로 고장확률은 $1 - e^{-0.004}$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지수분포의 신뢰도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신뢰도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R ( t ) = e^{-\lambda t}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;고장률이 일정할 때&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;고장확률(불신뢰도)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$F ( t ) = 1 - e^{-\lambda t}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$\lambda t$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.0004 × 10 = 0.004&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;MTBF&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{1}{\lambda} = 2 {,} 500$ 시간&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH33" s="32" t="inlineStr">
         <is>
-          <t>① $1 + e^{0.04}$ 는 부호와 지수가 모두 어긋난다.&lt;br&gt;③ $1 - e^{0.04}$ 는 지수의 부호가 빠졌다.&lt;br&gt;④ $1 - e^{-0.00004}$ 는 자릿수가 어긋난다.</t>
+          <t>① $1 + e^{0.04}$는 부호와 지수가 모두 어긋난다.&lt;br&gt;③ $1 - e^{0.04}$는 지수의 부호가 빠졌다.&lt;br&gt;④ $1 - e^{-0.00004}$는 자릿수가 어긋난다.</t>
         </is>
       </c>
       <c r="AI33" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지수분포의 고장확률&lt;/strong&gt;&lt;br&gt;$\lambda t$&lt;strong&gt; 를 먼저 셈하면 0.0004 × 10 = 0.004&lt;/strong&gt;다 — &lt;strong&gt;보기에 0.04 와 0.00004 가 함께 놓여 자릿수를 흔든다&lt;/strong&gt;. &lt;strong&gt;지수는 반드시 음수&lt;/strong&gt;라는 점도 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $F ( t ) = 1 - e^{-\lambda t}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지수분포의 고장확률&lt;/strong&gt;&lt;br&gt;$\lambda t$&lt;strong&gt;를 먼저 셈하면 0.0004 × 10 = 0.004&lt;/strong&gt;다 — &lt;strong&gt;보기에 0.04와 0.00004가 함께 놓여 자릿수를 흔든다&lt;/strong&gt;. &lt;strong&gt;지수는 반드시 음수&lt;/strong&gt;라는 점도 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $F ( t ) = 1 - e^{-\lambda t}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="AG35" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시간당 10회 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「5회 이상」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근골격계부담작업 11가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 4시간 이상 집중적으로 키보드·마우스 조작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 목·어깨·팔꿈치·손목·손을 사용해 같은 동작을 반복&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 머리 위에 손이 있거나 팔꿈치가 어깨 위에 있는 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 목이나 허리를 구부리거나 트는 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 쪼그리고 앉거나 무릎을 굽힌 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 지지 없이 1 [kg] 이상을 손가락으로 집는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 지지 없이 4.5 [kg] 이상을 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 10회 이상 25 [kg] 이상의 물체를 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 25회 이상 10 [kg] 이상의 물체를 무릎 아래·어깨 위·팔 뻗은 상태에서 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 4.5 [kg] 이상을 한 손으로 들거나 동일한 힘으로 쥐는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;11&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 시간당 10회 이상 손 또는 무릎으로 반복 충격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「5회」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;시간당 10회 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「5회 이상」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;근골격계부담작업 11가지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;작업&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 4시간 이상 집중적으로 키보드·마우스 조작&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;④&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 목·어깨·팔꿈치·손목·손을 사용해 같은 동작을 반복&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 머리 위에 손이 있거나 팔꿈치가 어깨 위에 있는 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 목이나 허리를 구부리거나 트는 상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 쪼그리고 앉거나 무릎을 굽힌 자세&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;②&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 지지 없이 1 [kg] 이상을 손가락으로 집는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 지지 없이 4.5 [kg] 이상을 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;8&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 10회 이상 25 [kg] 이상의 물체를 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;①&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 25회 이상 10 [kg] 이상의 물체를 무릎 아래·어깨 위·팔 뻗은 상태에서 드는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;10&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 4.5 [kg] 이상을 한 손으로 들거나 동일한 힘으로 쥐는 작업&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;11&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;하루 총 2시간 이상 시간당 10회 이상 손 또는 무릎으로 반복 충격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「5회」가 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH35" s="32" t="inlineStr">
@@ -5688,17 +5688,17 @@
       </c>
       <c r="AG36" s="32" t="inlineStr">
         <is>
-          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 35 + 0.15 \times 30 = 34.25$ [℃] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옥스퍼드 지수(WD)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스퍼드 지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$WD = 0.85 W + 0.15 D$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W 는 습구, D 는 건구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.85 × 35 + 0.15 × 30 = 34.25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계수를 뒤바꾸면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.85 × 30 + 0.15 × 35 = 30.75&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③으로 끌린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습건구 온도의 가중평균&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;습구에 크게 기운다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$WD = 0.85 W + 0.15 D = 0.85 \times 35 + 0.15 \times 30 = 34.25$ [℃]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;옥스퍼드 지수(WD)&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;옥스퍼드 지수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$WD = 0.85 W + 0.15 D$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;W는 습구, D는 건구&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.85 × 35 + 0.15 × 30 = 34.25&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;계수를 뒤바꾸면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.85 × 30 + 0.15 × 35 = 30.75&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;③으로 끌린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;뜻&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;습건구 온도의 가중평균&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;습구에 크게 기운다&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH36" s="32" t="inlineStr">
         <is>
-          <t>① 20.75 는 계산과 맞지 않는다.&lt;br&gt;② 24.58 도 그렇다.&lt;br&gt;③ 30.75 는 두 계수를 뒤바꾼 값이다.</t>
+          <t>① 20.75는 계산과 맞지 않는다.&lt;br&gt;② 24.58 도 그렇다.&lt;br&gt;③ 30.75는 두 계수를 뒤바꾼 값이다.</t>
         </is>
       </c>
       <c r="AI36" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;옥스퍼드 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;계수 0.85 가 습구에 붙는다&lt;/strong&gt; — &lt;strong&gt;더울 때 사람을 괴롭히는 것은 온도보다 습도&lt;/strong&gt; 이기 때문이다. &lt;strong&gt;뒤바꾼 값이 보기에 함께 놓여&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;옥스퍼드 지수&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;계수 0.85가 습구에 붙는다&lt;/strong&gt; — &lt;strong&gt;더울 때 사람을 괴롭히는 것은 온도보다 습도&lt;/strong&gt; 이기 때문이다. &lt;strong&gt;뒤바꾼 값이 보기에 함께 놓여&lt;/strong&gt; 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;습구 0.85, 건구 0.15&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -5817,12 +5817,12 @@
       </c>
       <c r="AG37" s="32" t="inlineStr">
         <is>
-          <t>순음의 청각신호는 &lt;strong&gt;0.5초 이상&lt;/strong&gt; 지속해야 한다. &lt;strong&gt;귀가 순음에 즉각 반응하지 않기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;청각적 표시장치의 설계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신호의 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀 위치에서 110 [dB] 과 은폐가청 역치의 중간쯤&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지속시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순음은 0.5초 이상&lt;/u&gt; — 「0.2초 이내」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작을수록 차원의 변화를 쉽게 알아챈다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다차원 암호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차원의 수를 늘리고 수준의 수를 줄이는 편이 식별이 쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 ~ 3,000 [Hz]&lt;/u&gt; — 멀리 보낼 때는 1,000 [Hz] 아래&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>순음의 청각신호는 &lt;strong&gt;0.5초 이상&lt;/strong&gt; 지속해야 한다. &lt;strong&gt;귀가 순음에 즉각 반응하지 않기&lt;/strong&gt; 때문이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;청각적 표시장치의 설계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;신호의 강도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;귀 위치에서 110 [dB]과 은폐가청 역치의 중간쯤&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지속시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;순음은 0.5초 이상&lt;/u&gt; — 「0.2초 이내」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;JND&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;작을수록 차원의 변화를 쉽게 알아챈다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;다차원 암호&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차원의 수를 늘리고 수준의 수를 줄이는 편이 식별이 쉽다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주파수&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;500 ~ 3,000 [Hz]&lt;/u&gt; — 멀리 보낼 때는 1,000 [Hz] 아래&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH37" s="32" t="inlineStr">
         <is>
-          <t>① 신호의 강도를 110 [dB] 과 은폐가청 역치의 중간쯤으로 하는 것은 맞다.&lt;br&gt;③ JND 가 작을수록 변화를 쉽게 알아채는 것도 맞다.&lt;br&gt;④ 차원의 수를 늘리고 수준의 수를 줄이는 편이 식별이 쉬운 것도 맞다.</t>
+          <t>① 신호의 강도를 110 [dB]과 은폐가청 역치의 중간쯤으로 하는 것은 맞다.&lt;br&gt;③ JND가 작을수록 변화를 쉽게 알아채는 것도 맞다.&lt;br&gt;④ 차원의 수를 늘리고 수준의 수를 줄이는 편이 식별이 쉬운 것도 맞다.</t>
         </is>
       </c>
       <c r="AI37" s="32" t="inlineStr">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="AG38" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;작업 조건의 분석&lt;/strong&gt;은 6단계에 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토(작성준비)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도면 · 목록 · 물성 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계관계 · 운전관계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물질 · 용량 · 온도 · 압력 · 조작&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비적 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA 에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;작업 조건의 분석&lt;/strong&gt;은 6단계에 들지 않는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전성 평가의 6단계&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;관계 자료의 정비검토(작성준비)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;도면 · 목록 · 물성 자료&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정성적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설계관계 · 운전관계&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;3&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정량적 평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;물질 · 용량 · 온도 · 압력 · 조작&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안전대책&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;설비적 대책 · 관리적 대책&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;재해정보에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;6&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;FTA에 의한 재평가&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH38" s="32" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="AH39" s="32" t="inlineStr">
         <is>
-          <t>① 2 [dB] 는 계산과 맞지 않는다.&lt;br&gt;② 3 [dB] 는 선음원의 값이다.&lt;br&gt;④ 9 [dB] 도 맞지 않는다.</t>
+          <t>① 2 [dB]는 계산과 맞지 않는다.&lt;br&gt;② 3 [dB]는 선음원의 값이다.&lt;br&gt;④ 9 [dB] 도 맞지 않는다.</t>
         </is>
       </c>
       <c r="AI39" s="32" t="inlineStr">
@@ -6214,7 +6214,7 @@
       </c>
       <c r="AI40" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;감각의 반응시간&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「청 · 촉 · 시 · 미 · 통」&lt;/strong&gt; 순으로 느려진다 — &lt;strong&gt;경보를 소리로 주는 까닭&lt;/strong&gt;이다. &lt;strong&gt;네 값이 0.17 · 0.18 · 0.20 으로 아주 가깝다&lt;/strong&gt;는 점도 눈여겨본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;청각이 가장 빠르다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;감각의 반응시간&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「청 · 촉 · 시 · 미 · 통」&lt;/strong&gt; 순으로 느려진다 — &lt;strong&gt;경보를 소리로 주는 까닭&lt;/strong&gt;이다. &lt;strong&gt;네 값이 0.17 · 0.18 · 0.20으로 아주 가깝다&lt;/strong&gt;는 점도 눈여겨본다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;청각이 가장 빠르다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
       </c>
       <c r="AI41" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;경고등의 설계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;경고는 「하나를 · 눈에 띄게 · 잘 보이는 자리에 · 빠르게 깜박이게」&lt;/strong&gt; 하는 것이다 — &lt;strong&gt;보기 셋이 그 넷을 하나씩 뒤집어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;배경보다 2배 이상 밝게&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;경고등의 설계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;경고는 「하나를 · 눈에 띄게 · 잘 보이는 자리에 · 빠르게 깜박이게」&lt;/strong&gt;하는 것이다 — &lt;strong&gt;보기 셋이 그 넷을 하나씩 뒤집어&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;배경보다 2배 이상 밝게&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6466,17 +6466,17 @@
       </c>
       <c r="AG42" s="32" t="inlineStr">
         <is>
-          <t>병렬부는 $1 - ( 1 - 0.7 )^{2} = 0.91$ 이다. 전체는 $0.91 \times 0.8 \times 0.8 = 0.5824$ 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;신뢰도의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 병렬부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - 0.3 \times 0.3 = 0.91$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7 두 개가 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.91 × 0.8 × 0.8 = 0.5824&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = R_{1} \times R_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>병렬부는 $1 - ( 1 - 0.7 )^{2} = 0.91$이다. 전체는 $0.91 \times 0.8 \times 0.8 = 0.5824$다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;신뢰도의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 병렬부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$1 - 0.3 \times 0.3 = 0.91$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.7 두 개가 병렬&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.91 × 0.8 × 0.8 = 0.5824&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;직렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = R_{1} \times R_{2} \times \cdots$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;병렬&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$R = 1 - ( 1 - R_{1} ) ( 1 - R_{2} )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH42" s="32" t="inlineStr">
         <is>
-          <t>② 0.6682 는 계산과 맞지 않는다.&lt;br&gt;③ 0.7855 도 그렇다.&lt;br&gt;④ 0.8642 도 그렇다.</t>
+          <t>② 0.6682는 계산과 맞지 않는다.&lt;br&gt;③ 0.7855 도 그렇다.&lt;br&gt;④ 0.8642 도 그렇다.</t>
         </is>
       </c>
       <c r="AI42" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;시스템의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬로 묶으면 0.7 두 개가 0.91 로 올라간다&lt;/strong&gt; — &lt;strong&gt;둘 다 죽어야 끊기므로&lt;/strong&gt; 그렇다. &lt;strong&gt;그 뒤로는 직렬이라 곱하기만 하면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬 먼저, 직렬 나중&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;시스템의 신뢰도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;병렬로 묶으면 0.7 두 개가 0.91로 올라간다&lt;/strong&gt; — &lt;strong&gt;둘 다 죽어야 끊기므로&lt;/strong&gt; 그렇다. &lt;strong&gt;그 뒤로는 직렬이라 곱하기만 하면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;병렬 먼저, 직렬 나중&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AG44" s="32" t="inlineStr">
         <is>
-          <t>밀링의 칩은 &lt;strong&gt;브러시로 제거&lt;/strong&gt; 한다. &lt;strong&gt;칩 브레이커는 선반의 부속&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;밀링작업의 안전조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절삭유는 가공부에서 떨어진 커터 위쪽에서 준다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급속이송은 백래시 제거장치가 작동하지 않음을 확인한 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩 제거는 브러시로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「칩 브레이커」가 아니다&lt;/u&gt; — 칩 브레이커는 선반의 부속&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이송장치의 핸들은 사용 뒤 풀어 놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주축 변속은 주축이 멈춘 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>밀링의 칩은 &lt;strong&gt;브러시로 제거&lt;/strong&gt;한다. &lt;strong&gt;칩 브레이커는 선반의 부속&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;밀링작업의 안전조치&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;절삭유는 가공부에서 떨어진 커터 위쪽에서 준다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;급속이송은 백래시 제거장치가 작동하지 않음을 확인한 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;칩 제거는 브러시로&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「칩 브레이커」가 아니다&lt;/u&gt; — 칩 브레이커는 선반의 부속&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이송장치의 핸들은 사용 뒤 풀어 놓는다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주축 변속은 주축이 멈춘 뒤에&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH44" s="32" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="AG46" s="32" t="inlineStr">
         <is>
-          <t>$T_{m} = ( \dfrac{1}{4} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{300} = 0.75 \times 200 = 150$ [ms] 다. $D = 1.6 \times 150 = 240$ [mm] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양수기동식 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1행정 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{60 {,} 000}{\mathrm{SPM}} = 200$ [ms]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;SPM 300&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times 200 = 150$ [ms]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;클러치 4개&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m} = 240$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$T_{m} = ( \dfrac{1}{4} + \dfrac{1}{2} ) \times \dfrac{60 {,} 000}{300} = 0.75 \times 200 = 150$ [ms]다. $D = 1.6 \times 150 = 240$ [mm]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;양수기동식 방호장치의 안전거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1행정 시간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{60 {,} 000}{\mathrm{SPM}} = 200$ [ms]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;SPM 300&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;$T_{m}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$( \dfrac{1}{\text{클러치 개소수}} + \dfrac{1}{2} ) \times 200 = 150$ [ms]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;클러치 4개&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$D = 1.6 T_{m} = 240$ [mm]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH46" s="32" t="inlineStr">
         <is>
-          <t>① 360 [mm] 는 계산과 맞지 않는다.&lt;br&gt;② 315 [mm] 도 그렇다.&lt;br&gt;④ 225 [mm] 도 그렇다.</t>
+          <t>① 360 [mm]는 계산과 맞지 않는다.&lt;br&gt;② 315 [mm] 도 그렇다.&lt;br&gt;④ 225 [mm] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI46" s="32" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="AH53" s="32" t="inlineStr">
         <is>
-          <t>① 다리는 500 [mm] 가 아니라 180 [mm] 다.&lt;br&gt;② 발은 300 [mm] 가 아니라 120 [mm] 다.&lt;br&gt;③ 손목은 200 [mm] 가 아니라 100 [mm] 다.</t>
+          <t>① 다리는 500 [mm]가 아니라 180 [mm]다.&lt;br&gt;② 발은 300 [mm]가 아니라 120 [mm]다.&lt;br&gt;③ 손목은 200 [mm]가 아니라 100 [mm]다.</t>
         </is>
       </c>
       <c r="AI53" s="32" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="U59" s="32" t="inlineStr">
         <is>
-          <t>지게차의 높이가 6m 이고, 안정도가 30%일 때 지게차의 수평거리는 얼마인가?</t>
+          <t>지게차의 높이가 6m이고, 안정도가 30%일 때 지게차의 수평거리는 얼마인가?</t>
         </is>
       </c>
       <c r="V59" s="32" t="inlineStr"/>
@@ -8659,17 +8659,17 @@
       </c>
       <c r="AG59" s="32" t="inlineStr">
         <is>
-          <t>$\text{안정도} = \dfrac{\text{높이}}{\text{수평거리}} \times 100$ 이므로 $\dfrac{6}{L} = 0.3$, $L = 20$ [m] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{높이} ( H )}{\text{수평거리} ( L )} \times 100$ [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수평거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L = \dfrac{H}{\text{안정도}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 6 ÷ 0.3 = 20 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$\text{안정도} = \dfrac{\text{높이}}{\text{수평거리}} \times 100$이므로 $\dfrac{6}{L} = 0.3$, $L = 20$ [m]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;지게차의 안정도&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안정도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{높이} ( H )}{\text{수평거리} ( L )} \times 100$ [%]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수평거리&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$L = \dfrac{H}{\text{안정도}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항 — 6 ÷ 0.3 = 20 [m]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;주행 시 전후&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하역작업 시 좌우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6% 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH59" s="32" t="inlineStr">
         <is>
-          <t>① 10 [m] 는 계산과 맞지 않는다.&lt;br&gt;③ 30 [m] 도 그렇다.&lt;br&gt;④ 40 [m] 도 그렇다.</t>
+          <t>① 10 [m]는 계산과 맞지 않는다.&lt;br&gt;③ 30 [m] 도 그렇다.&lt;br&gt;④ 40 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI59" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지게차의 안정도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30% 는 0.3&lt;/strong&gt;이다 — &lt;strong&gt;백분율을 그대로 나누면 6/30 = 0.2 이 나와 자릿수가 어긋난다&lt;/strong&gt;. &lt;strong&gt;「%」를 소수로 바꾸는 데서&lt;/strong&gt; 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수평거리 = 높이 ÷ 안정도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;지게차의 안정도&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;30%는 0.3&lt;/strong&gt;이다 — &lt;strong&gt;백분율을 그대로 나누면 6/30 = 0.2이 나와 자릿수가 어긋난다&lt;/strong&gt;. &lt;strong&gt;「%」를 소수로 바꾸는 데서&lt;/strong&gt; 갈린다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;수평거리 = 높이 ÷ 안정도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8788,17 +8788,17 @@
       </c>
       <c r="AG60" s="32" t="inlineStr">
         <is>
-          <t>동하중은 $\dfrac{4 {,} 000}{9.8} \times 2 \fallingdotseq 816$ [kgf] 다. 총하중은 $4 {,} 000 + 816 = 4 {,} 816$ [kgf] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;총하중의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정하중 + 동하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{정하중}}{g} \times a$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;g = 9.8 [m/s²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4,000 + (4,000/9.8) × 2 = 4,816 [kgf]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[N] 으로 물으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g + a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>동하중은 $\dfrac{4 {,} 000}{9.8} \times 2 \fallingdotseq 816$ [kgf]다. 총하중은 $4 {,} 000 + 816 = 4 {,} 816$ [kgf]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;총하중의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;총하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정하중 + 동하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;동하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$\dfrac{\text{정하중}}{g} \times a$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;g = 9.8 [m/s²]&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;4,000 + (4,000/9.8) × 2 = 4,816 [kgf]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;[N]으로 물으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$T = m ( g + a )$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH60" s="32" t="inlineStr">
         <is>
-          <t>① 약 4,063 [kgf] 는 계산과 맞지 않는다.&lt;br&gt;② 약 4,193 [kgf] 도 그렇다.&lt;br&gt;③ 약 4,243 [kgf] 도 그렇다.</t>
+          <t>① 약 4,063 [kgf]는 계산과 맞지 않는다.&lt;br&gt;② 약 4,193 [kgf] 도 그렇다.&lt;br&gt;③ 약 4,243 [kgf] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI60" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;와이어로프에 걸리는 총하중&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단위가 [kgf] 이면 중력가속도로 한 번 나눠&lt;/strong&gt; 야 한다 — &lt;strong&gt;[N] 으로 물으면 &lt;/strong&gt;$m ( g + a )$&lt;strong&gt; 로 곧바로&lt;/strong&gt; 셈한다. &lt;strong&gt;단위를 먼저 보는 것&lt;/strong&gt;이 요령이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;동하중 = (정하중/g) × a&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;와이어로프에 걸리는 총하중&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;단위가 [kgf] 이면 중력가속도로 한 번 나눠&lt;/strong&gt; 야 한다 — &lt;strong&gt;[N]으로 물으면 &lt;/strong&gt;$m ( g + a )$&lt;strong&gt;로 곧바로&lt;/strong&gt; 셈한다. &lt;strong&gt;단위를 먼저 보는 것&lt;/strong&gt;이 요령이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;동하중 = (정하중/g) × a&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -8917,7 +8917,7 @@
       </c>
       <c r="AG61" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;지름 4mm 이상의 와이어로프&lt;/strong&gt; 라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;급정지장치 조작부의 로프 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재질과 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 4mm 이상의 와이어로프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;또는 지름 6mm 이상이고 절단하중 2.94kN 이상의 합성섬유로프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사용 중에 늘어져서는 안 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충분한 인장강도를 가져야 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식 방호장치의 수인끈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합성섬유로 지름 4mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프레스 쪽 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;지름 4mm 이상의 와이어로프&lt;/strong&gt;라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;급정지장치 조작부의 로프 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;재질과 지름&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;지름 4mm 이상의 와이어로프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;또는 지름 6mm 이상이고 절단하중 2.94kN 이상의 합성섬유로프&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td rowspan="2" style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상태&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;사용 중에 늘어져서는 안 된다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;충분한 인장강도를 가져야 한다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;수인식 방호장치의 수인끈&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;합성섬유로 지름 4mm 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프레스 쪽 기준&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH61" s="32" t="inlineStr">
@@ -9404,7 +9404,7 @@
       </c>
       <c r="V65" s="32" t="inlineStr">
         <is>
-          <t>단, 심실세동전류는 $I = \dfrac{165}{\sqrt{T}}$ [mA] 로 한다.</t>
+          <t>단, 심실세동전류는 $I = \dfrac{165}{\sqrt{T}}$ [mA]로 한다.</t>
         </is>
       </c>
       <c r="W65" s="32" t="inlineStr"/>
@@ -9437,17 +9437,17 @@
       </c>
       <c r="AG65" s="32" t="inlineStr">
         <is>
-          <t>$W = I^{2} R T = ( 0.165 )^{2} \times 500 \fallingdotseq 13.6$ [J] 이다. &lt;strong&gt;통전시간에 따라 대략 6.5 ~ 17.0 [J]&lt;/strong&gt; 범위에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;달지엘의 식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T = ( 0.165 )^{2} R$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통전시간이 약분된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5 ~ 17.0 [J] 범위 안&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$W = I^{2} R T = ( 0.165 )^{2} \times 500 \fallingdotseq 13.6$ [J]이다. &lt;strong&gt;통전시간에 따라 대략 6.5 ~ 17.0 [J]&lt;/strong&gt; 범위에 든다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;위험한계 에너지&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;식&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;달지엘의 식&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;위험한계 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = I^{2} R T = ( 0.165 )^{2} R$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;통전시간이 약분된다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 500 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;13.6 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;6.5 ~ 17.0 [J] 범위 안&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;R = 1,000 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;27.23 [J]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH65" s="32" t="inlineStr">
         <is>
-          <t>② 2.5 ~ 3.0 [J] 는 지나치게 작다.&lt;br&gt;③ 650 ~ 1,700 [mJ] 는 0.65 ~ 1.7 [J] 로 자릿수가 어긋난다.&lt;br&gt;④ 250 ~ 300 [mJ] 도 그렇다.</t>
+          <t>② 2.5 ~ 3.0 [J]는 지나치게 작다.&lt;br&gt;③ 650 ~ 1,700 [mJ]는 0.65 ~ 1.7 [J]로 자릿수가 어긋난다.&lt;br&gt;④ 250 ~ 300 [mJ] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI65" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 ③④는 [mJ] 단위&lt;/strong&gt;라 &lt;strong&gt;[J] 로 고치면 1 도 안 되는 값&lt;/strong&gt;이다 — &lt;strong&gt;단위만 보아도 절반이 걸러진다&lt;/strong&gt;. &lt;strong&gt;13.6 [J] 가 들어가는 범위&lt;/strong&gt;를 고른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;위험한계 에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;보기 ③④는 [mJ] 단위&lt;/strong&gt;라 &lt;strong&gt;[J]로 고치면 1 도 안 되는 값&lt;/strong&gt;이다 — &lt;strong&gt;단위만 보아도 절반이 걸러진다&lt;/strong&gt;. &lt;strong&gt;13.6 [J]가 들어가는 범위&lt;/strong&gt;를 고른다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;500 [Ω] 이면 13.6 [J]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9566,7 +9566,7 @@
       </c>
       <c r="AG66" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;「통전망」은 전기가 통하는 그물&lt;/strong&gt;이라 오히려 위험하다. &lt;strong&gt;절연 방호망&lt;/strong&gt; 이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전사고 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비의 필요한 부분에 보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노출 충전부에 절연용 방호망이나 절연덮개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「통전망」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전전압 이하의 기기 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;우리나라 안전전압 30 [V]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전기기기와 설비의 정비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연구조 · 누전차단기 설치 · 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;「통전망」은 전기가 통하는 그물&lt;/strong&gt;이라 오히려 위험하다. &lt;strong&gt;절연 방호망&lt;/strong&gt;이라야 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;감전사고 방지대책&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대책&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;설비의 필요한 부분에 보호접지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;노출 충전부에 절연용 방호망이나 절연덮개&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「통전망」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전전압 이하의 기기 사용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;우리나라 안전전압 30 [V]&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전기기기와 설비의 정비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이중절연구조 · 누전차단기 설치 · 보호구 착용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH66" s="32" t="inlineStr">
@@ -9661,7 +9661,7 @@
       </c>
       <c r="U67" s="32" t="inlineStr">
         <is>
-          <t>인체의 전격시의 통전시간이 4초 일 때 심실세동 전류를 Dalziel 이 주장한 식으로 계산한 것으로 다음 중 알맞은 것은?</t>
+          <t>인체의 전격시의 통전시간이 4초 일 때 심실세동 전류를 Dalziel이 주장한 식으로 계산한 것으로 다음 중 알맞은 것은?</t>
         </is>
       </c>
       <c r="V67" s="32" t="inlineStr"/>
@@ -9695,17 +9695,17 @@
       </c>
       <c r="AG67" s="32" t="inlineStr">
         <is>
-          <t>$I = \dfrac{165}{\sqrt{4}} = \dfrac{165}{2} = 82.5$ [mA] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;통전시간 T [초]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;심실세동전류 [mA]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;165&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;116.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;82.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;55&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;T 는 1초 ~ 3초에서 유효&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>$I = \dfrac{165}{\sqrt{4}} = \dfrac{165}{2} = 82.5$ [mA]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;심실세동전류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;통전시간 T [초]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;심실세동전류 [mA]&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;165&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;2&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;116.7&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;4&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;82.5&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이 문항&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;9&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;55&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I = \dfrac{165}{\sqrt{T}}$&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;T는 1초 ~ 3초에서 유효&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH67" s="32" t="inlineStr">
         <is>
-          <t>① 53 [mA] 는 계산과 맞지 않는다.&lt;br&gt;③ 102.5 [mA] 도 그렇다.&lt;br&gt;④ 143 [mA] 도 그렇다.</t>
+          <t>① 53 [mA]는 계산과 맞지 않는다.&lt;br&gt;③ 102.5 [mA] 도 그렇다.&lt;br&gt;④ 143 [mA] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI67" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;달지엘의 심실세동전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 「T」가 아니라 「√T」&lt;/strong&gt;다 — &lt;strong&gt;4 를 그대로 나누면 41.25 가 되고, 제곱근 2 로 나눠야 82.5&lt;/strong&gt;다. &lt;strong&gt;시간이 길어질수록 견딜 수 있는 전류가 작아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = 165 / \sqrt{T}$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;달지엘의 심실세동전류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;분모가 「T」가 아니라 「√T」&lt;/strong&gt;다 — &lt;strong&gt;4를 그대로 나누면 41.25가 되고, 제곱근 2로 나눠야 82.5&lt;/strong&gt;다. &lt;strong&gt;시간이 길어질수록 견딜 수 있는 전류가 작아진다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; $I = 165 / \sqrt{T}$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -9926,25 +9926,25 @@
       <c r="W69" s="32" t="inlineStr"/>
       <c r="X69" s="32" t="inlineStr">
         <is>
-          <t>남녀 모두 직류 5.2[mA]이며, 교류(평균치) 1.1[mA] 이다.</t>
+          <t>남녀 모두 직류 5.2[mA]이며, 교류(평균치) 1.1[mA]이다.</t>
         </is>
       </c>
       <c r="Y69" s="32" t="inlineStr"/>
       <c r="Z69" s="32" t="inlineStr">
         <is>
-          <t>남자의 경우 직류 5.2[mA]이며, 교류(실효치) 1.1[mA] 이다.</t>
+          <t>남자의 경우 직류 5.2[mA]이며, 교류(실효치) 1.1[mA]이다.</t>
         </is>
       </c>
       <c r="AA69" s="32" t="inlineStr"/>
       <c r="AB69" s="32" t="inlineStr">
         <is>
-          <t>남녀 모두 직류 3.5[mA]이며, 교류(실효치) 1.1[mA] 이다.</t>
+          <t>남녀 모두 직류 3.5[mA]이며, 교류(실효치) 1.1[mA]이다.</t>
         </is>
       </c>
       <c r="AC69" s="32" t="inlineStr"/>
       <c r="AD69" s="32" t="inlineStr">
         <is>
-          <t>여자의 경우 직류 3.5[mA]이며, 교류(평균치) 0.7[mA] 이다.</t>
+          <t>여자의 경우 직류 3.5[mA]이며, 교류(평균치) 0.7[mA]이다.</t>
         </is>
       </c>
       <c r="AE69" s="32" t="inlineStr"/>
@@ -9958,7 +9958,7 @@
       </c>
       <c r="AH69" s="32" t="inlineStr">
         <is>
-          <t>① 남녀의 값이 같지 않고, 교류는 평균치가 아니라 실효치다.&lt;br&gt;③ 남녀 모두 직류 3.5 [mA] 라는 것도 맞지 않는다.&lt;br&gt;④ 여자의 교류값은 평균치가 아니라 실효치 0.7 [mA] 다.</t>
+          <t>① 남녀의 값이 같지 않고, 교류는 평균치가 아니라 실효치다.&lt;br&gt;③ 남녀 모두 직류 3.5 [mA]라는 것도 맞지 않는다.&lt;br&gt;④ 여자의 교류값은 평균치가 아니라 실효치 0.7 [mA]다.</t>
         </is>
       </c>
       <c r="AI69" s="32" t="inlineStr">
@@ -10053,7 +10053,7 @@
       </c>
       <c r="V70" s="32" t="inlineStr">
         <is>
-          <t>단, 심실세동전류는 $I_{k} = \dfrac{165}{\sqrt{T}}$ [mA] 이며, 인체저항 $R_{k} = 1 {,} 000$ [Ω], 발의 저항 $R_{f} = 300$ [Ω] 이고, 접촉 시간은 1초로 한다.</t>
+          <t>단, 심실세동전류는 $I_{k} = \dfrac{165}{\sqrt{T}}$ [mA]이며, 인체저항 $R_{k} = 1 {,} 000$ [Ω], 발의 저항 $R_{f} = 300$ [Ω]이고, 접촉 시간은 1초로 한다.</t>
         </is>
       </c>
       <c r="W70" s="32" t="inlineStr">
@@ -10090,17 +10090,17 @@
       </c>
       <c r="AG70" s="32" t="inlineStr">
         <is>
-          <t>두 발은 병렬이므로 $R_{f} / 2 = 150$ [Ω] 이다. $E = I_{k} ( R_{k} + \dfrac{R_{f}}{2} ) = 0.165 \times 1 {,} 150 \fallingdotseq 190$ [V] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;허용접촉전압의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I_{k} = \dfrac{165}{\sqrt{1}} = 165$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 발 저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 발이 병렬이므로 300 ÷ 2 = 150 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 전체 저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 + 150 = 1,150 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ 허용접촉전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.165 × 1,150 = 190 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>두 발은 병렬이므로 $R_{f} / 2 = 150$ [Ω]이다. $E = I_{k} ( R_{k} + \dfrac{R_{f}}{2} ) = 0.165 \times 1 {,} 150 \fallingdotseq 190$ [V]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;허용접촉전압의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 심실세동전류&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$I_{k} = \dfrac{165}{\sqrt{1}} = 165$ [mA]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 발 저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;두 발이 병렬이므로 300 ÷ 2 = 150 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 전체 저항&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1,000 + 150 = 1,150 [Ω]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;④ 허용접촉전압&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.165 × 1,150 = 190 [V]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH70" s="32" t="inlineStr">
         <is>
-          <t>① 107 [V] 는 계산과 맞지 않는다.&lt;br&gt;② 132 [V] 도 그렇다.&lt;br&gt;④ 215 [V] 는 발 저항을 300 [Ω] 그대로 더한 값에 가깝다.</t>
+          <t>① 107 [V]는 계산과 맞지 않는다.&lt;br&gt;② 132 [V] 도 그렇다.&lt;br&gt;④ 215 [V]는 발 저항을 300 [Ω] 그대로 더한 값에 가깝다.</t>
         </is>
       </c>
       <c r="AI70" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;허용접촉전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 발이 나란히 땅을 딛고 있으므로 발 저항은 병렬&lt;/strong&gt;이다 — &lt;strong&gt;300 을 그대로 더하면 215 가 나와 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;보폭전압을 물으면 발이 직렬이라 &lt;/strong&gt;$R_{k} + 2 R_{f}$로 바뀐다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;접촉전압은 &lt;/u&gt;$R_{k} + R_{f} / 2$.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;허용접촉전압&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;두 발이 나란히 땅을 딛고 있으므로 발 저항은 병렬&lt;/strong&gt;이다 — &lt;strong&gt;300을 그대로 더하면 215가 나와 ④로 끌린다&lt;/strong&gt;. &lt;strong&gt;보폭전압을 물으면 발이 직렬이라 &lt;/strong&gt;$R_{k} + 2 R_{f}$로 바뀐다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;접촉전압은 &lt;/u&gt;$R_{k} + R_{f} / 2$.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10219,17 +10219,17 @@
       </c>
       <c r="AG71" s="32" t="inlineStr">
         <is>
-          <t>ⅡB 는 &lt;strong&gt;30 [mm]&lt;/strong&gt;다. &lt;strong&gt;「20 [mm]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내압방폭구조 d 의 이격거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 이격거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판 등&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌 등&lt;/u&gt; · 「20」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나사 접합부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;체결 나사산 5산 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압방폭 접합부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안의 폭발이 밖으로 번지지 않게 막는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>ⅡB는 &lt;strong&gt;30 [mm]&lt;/strong&gt;다. &lt;strong&gt;「20 [mm]」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내압방폭구조 d의 이격거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 이격거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판 등&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌 등&lt;/u&gt; · 「20」이 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;나사 접합부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;체결 나사산 5산 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압방폭 접합부&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안의 폭발이 밖으로 번지지 않게 막는 부분&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH71" s="32" t="inlineStr">
         <is>
-          <t>① 나사 접합부의 체결 나사산이 5산 이상인 것은 맞다.&lt;br&gt;③ 내압방폭 접합부의 정의도 맞다.&lt;br&gt;④ ⅡC 의 최소 이격거리가 40 [mm] 인 것도 맞다.</t>
+          <t>① 나사 접합부의 체결 나사산이 5산 이상인 것은 맞다.&lt;br&gt;③ 내압방폭 접합부의 정의도 맞다.&lt;br&gt;④ ⅡC의 최소 이격거리가 40 [mm] 인 것도 맞다.</t>
         </is>
       </c>
       <c r="AI71" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압방폭구조의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 30 · 40」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;폭발하기 쉬운 가스일수록(ⅡA → ⅡC) 멀리&lt;/strong&gt; 떼어 놓는다. &lt;strong&gt;ⅡB 를 20 으로 낮춰&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 10 · ⅡB 30 · ⅡC 40&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압방폭구조의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 · 30 · 40」&lt;/strong&gt; 세 값이다 — &lt;strong&gt;폭발하기 쉬운 가스일수록(ⅡA → ⅡC) 멀리&lt;/strong&gt; 떼어 놓는다. &lt;strong&gt;ⅡB를 20으로 낮춰&lt;/strong&gt; 놓았다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡA 10 · ⅡB 30 · ⅡC 40&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AG72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압방폭구조는 d&lt;/strong&gt;다. &lt;strong&gt;p 는 압력방폭구조&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안에서 터져도 밖으로 번지지 않게&lt;/u&gt; — 「p」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에 공기를 밀어 넣어&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름에 담가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전도를 더 높여&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia · ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에너지 자체를 낮춰&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;몰드 · 충전 · 비점화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;m · q · n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;내압방폭구조는 d&lt;/strong&gt;다. &lt;strong&gt;p는 압력방폭구조&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;방폭구조의 기호&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;구조&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기호&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;내압방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;d&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;안에서 터져도 밖으로 번지지 않게&lt;/u&gt; — 「p」가 아니다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;압력방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;p&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안에 공기를 밀어 넣어&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;유입방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;o&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;기름에 담가&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전증방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;e&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;안전도를 더 높여&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;본질안전방폭구조&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;ia · ib&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;에너지 자체를 낮춰&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;몰드 · 충전 · 비점화&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;m · q · n&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH72" s="32" t="inlineStr">
@@ -10358,7 +10358,7 @@
       </c>
       <c r="AI72" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기호는 대개 영어의 첫 글자&lt;/strong&gt;다 — &lt;strong&gt;pressurized(p) · oil(o) · increased safety(e) · intrinsic(i)&lt;/strong&gt;. &lt;strong&gt;내압은 flame-proof 의 d&lt;/strong&gt;라 예외처럼 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내압은 d, 압력이 p&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;방폭구조의 기호&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;기호는 대개 영어의 첫 글자&lt;/strong&gt;다 — &lt;strong&gt;pressurized(p) · oil(o) · increased safety(e) · intrinsic(i)&lt;/strong&gt;. &lt;strong&gt;내압은 flame-proof의 d&lt;/strong&gt;라 예외처럼 보인다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;내압은 d, 압력이 p&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10477,17 +10477,17 @@
       </c>
       <c r="AG73" s="32" t="inlineStr">
         <is>
-          <t>ⅡB 는 &lt;strong&gt;30 [mm]&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내압방폭구조 d 의 최소 이격거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 이격거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 가스&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판 · 메탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 떼어 놓나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접합면에서 뿜어 나온 뜨거운 가스가 장애물에 부딪혀 다시 모이면 밖에서 불붙을 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>ⅡB는 &lt;strong&gt;30 [mm]&lt;/strong&gt;다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;내압방폭구조 d의 최소 이격거리&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;가스 그룹&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;최소 이격거리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;대표 가스&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡA&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;10 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;프로판 · 메탄&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡB&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;30 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;에틸렌&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;ⅡC&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;40 [mm]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;수소 · 아세틸렌&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;왜 떼어 놓나&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;접합면에서 뿜어 나온 뜨거운 가스가 장애물에 부딪혀 다시 모이면 밖에서 불붙을 수 있다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH73" s="32" t="inlineStr">
         <is>
-          <t>① 10 [mm] 는 ⅡA 의 값이다.&lt;br&gt;② 20 [mm] 는 기준에 없는 값이다.&lt;br&gt;④ 40 [mm] 는 ⅡC 의 값이다.</t>
+          <t>① 10 [mm]는 ⅡA의 값이다.&lt;br&gt;② 20 [mm]는 기준에 없는 값이다.&lt;br&gt;④ 40 [mm]는 ⅡC의 값이다.</t>
         </is>
       </c>
       <c r="AI73" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;내압방폭기기의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;접합면의 좁은 틈으로 나온 화염은 식으면서 꺼진다&lt;/strong&gt; — &lt;strong&gt;장애물이 가까이 있으면 식기 전에 부딪혀 되돌아오므로 거리가 필요&lt;/strong&gt; 하다. &lt;strong&gt;위험한 가스일수록 멀리&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡB 는 30 [mm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;내압방폭기기의 이격거리&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;접합면의 좁은 틈으로 나온 화염은 식으면서 꺼진다&lt;/strong&gt; — &lt;strong&gt;장애물이 가까이 있으면 식기 전에 부딪혀 되돌아오므로 거리가 필요&lt;/strong&gt;하다. &lt;strong&gt;위험한 가스일수록 멀리&lt;/strong&gt; 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;ⅡB는 30 [mm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -10572,7 +10572,7 @@
       </c>
       <c r="U74" s="32" t="inlineStr">
         <is>
-          <t>인체의 표면적이 0.5m2이고 정전용량은 0.02pF/cm2 이다. 3300V의 전압이 인가되어 있는 전선에 접근하여 작업을 할 때 인체에 축척되는 정전기 에너지(J)는?</t>
+          <t>인체의 표면적이 0.5m2이고 정전용량은 0.02pF/cm2이다. 3300V의 전압이 인가되어 있는 전선에 접근하여 작업을 할 때 인체에 축척되는 정전기 에너지(J)는?</t>
         </is>
       </c>
       <c r="V74" s="32" t="inlineStr"/>
@@ -10606,17 +10606,17 @@
       </c>
       <c r="AG74" s="32" t="inlineStr">
         <is>
-          <t>정전용량은 $0.02 \times 5 {,} 000 = 100$ [pF] 다. $W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} \times 10^{-10} \times 3 {,} 300^{2} \fallingdotseq 5.445 \times 10^{-4}$ [J] 다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 면적 환산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [m²] = 5,000 [cm²]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 정전용량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.02 × 5,000 = 100 [pF] = 10⁻¹⁰ [F]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = 5.445 \times 10^{-4}$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1/2 을 빠뜨리면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.089 × 10⁻³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>정전용량은 $0.02 \times 5 {,} 000 = 100$ [pF]다. $W = \dfrac{1}{2} C V^{2} = \dfrac{1}{2} \times 10^{-10} \times 3 {,} 300^{2} \fallingdotseq 5.445 \times 10^{-4}$ [J]다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;정전기 에너지의 셈&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;단계&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;셈&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;① 면적 환산&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.5 [m²] = 5,000 [cm²]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;여기서 갈린다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;② 정전용량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;0.02 × 5,000 = 100 [pF] = 10⁻¹⁰ [F]&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;③ 에너지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;$W = \dfrac{1}{2} C V^{2} = 5.445 \times 10^{-4}$ [J]&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;1/2을 빠뜨리면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.089 × 10⁻³&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH74" s="32" t="inlineStr">
         <is>
-          <t>① 5.445 × 10⁻² 는 자릿수가 어긋난다.&lt;br&gt;③ 2.723 × 10⁻² 도 그렇다.&lt;br&gt;④ 2.723 × 10⁻⁴ 는 1/2 을 한 번 더 나눈 값이다.</t>
+          <t>① 5.445 × 10⁻² 는 자릿수가 어긋난다.&lt;br&gt;③ 2.723 × 10⁻² 도 그렇다.&lt;br&gt;④ 2.723 × 10⁻⁴ 는 1/2을 한 번 더 나눈 값이다.</t>
         </is>
       </c>
       <c r="AI74" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 [m²] 가 5,000 [cm²]&lt;/strong&gt;라는 환산이 첫 갈림길이다 — &lt;strong&gt;1 [m²] = 10,000 [cm²]&lt;/strong&gt;. &lt;strong&gt;그다음은 &lt;/strong&gt;$W = \dfrac{1}{2} C V^{2}$&lt;strong&gt; 에 그대로 넣으면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 [m²] = 10,000 [cm²]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기 방전에너지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;0.5 [m²]가 5,000 [cm²]&lt;/strong&gt;라는 환산이 첫 갈림길이다 — &lt;strong&gt;1 [m²] = 10,000 [cm²]&lt;/strong&gt;. &lt;strong&gt;그다음은 &lt;/strong&gt;$W = \dfrac{1}{2} C V^{2}$&lt;strong&gt;에 그대로 넣으면&lt;/strong&gt; 된다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;1 [m²] = 10,000 [cm²]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11003,7 +11003,7 @@
       </c>
       <c r="AI77" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;절연물의 종별&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「Y · A · E · B · F · H · C」&lt;/strong&gt; 일곱 글자를 차례로 외운다 — &lt;strong&gt;90 · 105 · 120 · 130 · 155 · 180 · 180 초과&lt;/strong&gt;다. &lt;strong&gt;C 가 알파벳 앞쪽이면서 가장 높다&lt;/strong&gt;는 점이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Y · A · E · B · F · H · C&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;절연물의 종별&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「Y · A · E · B · F · H · C」&lt;/strong&gt; 일곱 글자를 차례로 외운다 — &lt;strong&gt;90 · 105 · 120 · 130 · 155 · 180 · 180 초과&lt;/strong&gt;다. &lt;strong&gt;C가 알파벳 앞쪽이면서 가장 높다&lt;/strong&gt;는 점이 함정이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;Y · A · E · B · F · H · C&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="AI79" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;접지 시의 방전 위험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;접지는 정전기의 근본 대책이지만 「이미 쌓인 뒤에 잇는 것」은 위험&lt;/strong&gt; 하다 — &lt;strong&gt;전하가 한꺼번에 빠져나가며 불꽃&lt;/strong&gt;이 된다. &lt;strong&gt;미리 이어 두어 쌓이지 않게&lt;/strong&gt; 하는 것이 맞다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;쌓인 뒤에 접지하면 불꽃이 튄다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;접지 시의 방전 위험&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;접지는 정전기의 근본 대책이지만 「이미 쌓인 뒤에 잇는 것」은 위험&lt;/strong&gt;하다 — &lt;strong&gt;전하가 한꺼번에 빠져나가며 불꽃&lt;/strong&gt;이 된다. &lt;strong&gt;미리 이어 두어 쌓이지 않게&lt;/strong&gt; 하는 것이 맞다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;쌓인 뒤에 접지하면 불꽃이 튄다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11390,7 +11390,7 @@
       </c>
       <c r="AI80" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;등전위 접지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;심장에 직접 닿는 기기는 수십 [μA] 로도 위험&lt;/strong&gt; 하다 — &lt;strong&gt;그래서 「전위차를 0 으로」 만드는 등전위 접지&lt;/strong&gt;를 쓴다. &lt;strong&gt;「병원 · 의료」라는 낱말이 곧 등전위&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;의료용 기기는 등전위 접지&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;등전위 접지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;심장에 직접 닿는 기기는 수십 [μA] 로도 위험&lt;/strong&gt;하다 — &lt;strong&gt;그래서 「전위차를 0으로」 만드는 등전위 접지&lt;/strong&gt;를 쓴다. &lt;strong&gt;「병원 · 의료」라는 낱말이 곧 등전위&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;의료용 기기는 등전위 접지&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="AI81" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;정전기의 발생요인&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 요인이 모두 「닿는 면과 떨어지는 방식」&lt;/strong&gt;에 관한 것이다 — &lt;strong&gt;질량은 무게일 뿐 전하가 갈리는 것과 무관&lt;/strong&gt; 하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특성 · 표면 · 이력 · 면적압력 · 분리속도&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;정전기의 발생요인&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;다섯 요인이 모두 「닿는 면과 떨어지는 방식」&lt;/strong&gt;에 관한 것이다 — &lt;strong&gt;질량은 무게일 뿐 전하가 갈리는 것과 무관&lt;/strong&gt;하다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;특성 · 표면 · 이력 · 면적압력 · 분리속도&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -11638,7 +11638,7 @@
       </c>
       <c r="AG82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;전압인가식 제전기&lt;/strong&gt;다. &lt;strong&gt;방전침에 고전압을 걸어 이온을 만든다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;제전기의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압인가식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방전침에 약 7,000 [V] 를 걸어 코로나 방전으로 이온을 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전능력이 가장 크다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기방전식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대전체 자신의 전계로 방전시킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [kV] 안팎의 대전이 남는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사선식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선의 전리작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제전효율이 낮으나 폭발위험지역에 알맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이온스프레이식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이온을 바람으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;전압인가식 제전기&lt;/strong&gt;다. &lt;strong&gt;방전침에 고전압을 걸어 이온을 만든다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;제전기의 종류&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;종류&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;원리&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;전압인가식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방전침에 약 7,000 [V]를 걸어 코로나 방전으로 이온을 만든다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;제전능력이 가장 크다&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;자기방전식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;대전체 자신의 전계로 방전시킨다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;2 [kV] 안팎의 대전이 남는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;방사선식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;방사선의 전리작용&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;제전효율이 낮으나 폭발위험지역에 알맞다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이온스프레이식&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;이온을 바람으로 보낸다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH82" s="32" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="AI82" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;제전기의 종류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「7,000 [V] 를 인가」&lt;/strong&gt;라는 말이 그대로 전압인가식이다 — &lt;strong&gt;스스로 방전하면 자기방전식, 방사선을 쓰면 방사선식&lt;/strong&gt;으로 갈린다. &lt;strong&gt;제전능력은 전압인가식이 가장 크다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;방전침에 전압을 걸면 전압인가식&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;제전기의 종류&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「7,000 [V]를 인가」&lt;/strong&gt;라는 말이 그대로 전압인가식이다 — &lt;strong&gt;스스로 방전하면 자기방전식, 방사선을 쓰면 방사선식&lt;/strong&gt;으로 갈린다. &lt;strong&gt;제전능력은 전압인가식이 가장 크다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;방전침에 전압을 걸면 전압인가식&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12025,7 +12025,7 @@
       </c>
       <c r="AG85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;배출용량의 2분의 1 이상&lt;/strong&gt; 이라야 한다. &lt;strong&gt;「4분의 1」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차단밸브를 설치할 수 있는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인접한 설비에 안전밸브가 각각 있고 연결배관에 차단밸브가 없는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브 배출용량의 1/2 이상인 자동압력조절밸브와 직렬로 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1/4」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브가 복수방식으로 설치된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열팽창으로 오른 압력을 낮추려고 안전밸브를 단 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하나의 플레어스택에 둘 이상의 안전밸브 배출관이 이어진 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단밸브를 잠그면 안전밸브가 무용지물이 되므로 금지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;배출용량의 2분의 1 이상&lt;/strong&gt;이라야 한다. &lt;strong&gt;「4분의 1」이 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;차단밸브를 설치할 수 있는 경우&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;경우&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;인접한 설비에 안전밸브가 각각 있고 연결배관에 차단밸브가 없는 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브 배출용량의 1/2 이상인 자동압력조절밸브와 직렬로 연결된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「1/4」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;안전밸브가 복수방식으로 설치된 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열팽창으로 오른 압력을 낮추려고 안전밸브를 단 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하나의 플레어스택에 둘 이상의 안전밸브 배출관이 이어진 경우&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;원칙&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;차단밸브를 잠그면 안전밸브가 무용지물이 되므로 금지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH85" s="32" t="inlineStr">
@@ -12035,7 +12035,7 @@
       </c>
       <c r="AI85" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;안전밸브 앞뒤의 차단밸브&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차단밸브가 잠기면 안전밸브가 있으나 마나&lt;/strong&gt; 하다 — &lt;strong&gt;그래서 원칙은 금지이고, 「그래도 압력이 빠져나갈 다른 길이 있다」는 경우만 예외&lt;/strong&gt;다. &lt;strong&gt;그 길이 충분하려면 절반은 되어야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자동압력조절밸브는 배출용량의 1/2 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;안전밸브 앞뒤의 차단밸브&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;차단밸브가 잠기면 안전밸브가 있으나 마나&lt;/strong&gt;하다 — &lt;strong&gt;그래서 원칙은 금지이고, 「그래도 압력이 빠져나갈 다른 길이 있다」는 경우만 예외&lt;/strong&gt;다. &lt;strong&gt;그 길이 충분하려면 절반은 되어야&lt;/strong&gt; 한다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자동압력조절밸브는 배출용량의 1/2 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="AI88" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;폭발하한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한이 낮을수록 조금만 새도 위험&lt;/strong&gt; 하다 — &lt;strong&gt;이황화탄소 1.2 가 대표적으로 낮은 값&lt;/strong&gt;이다. &lt;strong&gt;메탄 5 가 넷 가운데 가장 높다&lt;/strong&gt;는 것만 알아도 ②③이 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CS₂ 1.2 &amp;lt; C₂H₂ 2.5 &amp;lt; H₂ 4 &amp;lt; CH₄ 5&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;폭발하한계&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;하한이 낮을수록 조금만 새도 위험&lt;/strong&gt;하다 — &lt;strong&gt;이황화탄소 1.2가 대표적으로 낮은 값&lt;/strong&gt;이다. &lt;strong&gt;메탄 5가 넷 가운데 가장 높다&lt;/strong&gt;는 것만 알아도 ②③이 걸러진다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;CS₂ 1.2 &amp;lt; C₂H₂ 2.5 &amp;lt; H₂ 4 &amp;lt; CH₄ 5&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -13062,7 +13062,7 @@
       </c>
       <c r="AH93" s="32" t="inlineStr">
         <is>
-          <t>② 암모니아는 25 [ppm] 이다.&lt;br&gt;③ 에탄올은 1,000 [ppm] 으로 넷 가운데 가장 높다.&lt;br&gt;④ 메탄올은 200 [ppm] 이다.</t>
+          <t>② 암모니아는 25 [ppm]이다.&lt;br&gt;③ 에탄올은 1,000 [ppm]으로 넷 가운데 가장 높다.&lt;br&gt;④ 메탄올은 200 [ppm]이다.</t>
         </is>
       </c>
       <c r="AI93" s="32" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="AH94" s="32" t="inlineStr">
         <is>
-          <t>① 25 [mg/kg] 은 기준값이 아니다.&lt;br&gt;② 100 [mg/kg] 도 그렇다.&lt;br&gt;④ 500 [mg/kg] 도 그렇다.</t>
+          <t>① 25 [mg/kg]은 기준값이 아니다.&lt;br&gt;② 100 [mg/kg] 도 그렇다.&lt;br&gt;④ 500 [mg/kg] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI94" s="32" t="inlineStr">
@@ -13969,7 +13969,7 @@
       </c>
       <c r="AH100" s="32" t="inlineStr">
         <is>
-          <t>① 10% 는 기준값이 아니다.&lt;br&gt;② 15% 도 그렇다.&lt;br&gt;④ 25% 도 그렇다.</t>
+          <t>① 10%는 기준값이 아니다.&lt;br&gt;② 15% 도 그렇다.&lt;br&gt;④ 25% 도 그렇다.</t>
         </is>
       </c>
       <c r="AI100" s="32" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="AI101" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연발화의 정의가 「점화원 없이 스스로 불붙는 것」&lt;/strong&gt;이다 — &lt;strong&gt;없는 것을 없앨 수는 없다&lt;/strong&gt;. &lt;strong&gt;방지법은 모두 「열이 쌓이지 않게」&lt;/strong&gt; 하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연발화에는 점화원이 없다&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;자연발화의 방지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;자연발화의 정의가 「점화원 없이 스스로 불붙는 것」&lt;/strong&gt;이다 — &lt;strong&gt;없는 것을 없앨 수는 없다&lt;/strong&gt;. &lt;strong&gt;방지법은 모두 「열이 쌓이지 않게」&lt;/strong&gt;하는 쪽이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;자연발화에는 점화원이 없다&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14360,7 +14360,7 @@
       </c>
       <c r="AH103" s="32" t="inlineStr">
         <is>
-          <t>② 6 [m] 는 기준값이 아니다.&lt;br&gt;③ 5 [m] 도 그렇다.&lt;br&gt;④ 4 [m] 도 그렇다.</t>
+          <t>② 6 [m]는 기준값이 아니다.&lt;br&gt;③ 5 [m] 도 그렇다.&lt;br&gt;④ 4 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI103" s="32" t="inlineStr">
@@ -14613,7 +14613,7 @@
       </c>
       <c r="AG105" s="32" t="inlineStr">
         <is>
-          <t>비계기둥 사이의 적재하중은 &lt;strong&gt;400 [kg]&lt;/strong&gt;을 넘지 않게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최고부에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개의 강관으로 묶어 세울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 사이의 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg] 을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「600 [kg]」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>비계기둥 사이의 적재하중은 &lt;strong&gt;400 [kg]&lt;/strong&gt;을 넘지 않게 한다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;강관비계의 구조&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 띠장 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.85 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 간격 — 장선 방향&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;띠장 간격&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2.0 [m] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;최고부에서 31 [m] 되는 지점 아래&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;2개의 강관으로 묶어 세울 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;비계기둥 사이의 적재하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;400 [kg]을 넘지 않을 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「600 [kg]」이 아니다&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH105" s="32" t="inlineStr">
@@ -14623,7 +14623,7 @@
       </c>
       <c r="AI105" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강관비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.85 · 1.5 · 2.0 · 31 · 400」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;400 [kg] 은 사람 넷과 자재의 무게&lt;/strong&gt; 쯤으로 새기면 600 이 지나침을 알 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비계기둥 사이 적재하중 400 [kg]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 띠장 방향 간격은 &lt;u&gt;2022.10.18 개정&lt;/u&gt;으로 &lt;u&gt;1.85 [m] 이하&lt;/u&gt;가 되었고, 선박·항공기 등 규격이 큰 구조물을 제작할 때에는 안전성 검토를 거쳐 &lt;u&gt;2.7 [m] 이하&lt;/u&gt;까지 넓힐 수 있다.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;강관비계의 구조&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「1.85 · 1.5 · 2.0 · 31 · 400」&lt;/strong&gt; 다섯 숫자다 — &lt;strong&gt;400 [kg]은 사람 넷과 자재의 무게&lt;/strong&gt; 쯤으로 새기면 600이 지나침을 알 수 있다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비계기둥 사이 적재하중 400 [kg]&lt;/u&gt;.&lt;/p&gt;&lt;p&gt;&lt;strong&gt;⚠ 주의사항&lt;/strong&gt; 띠장 방향 간격은 &lt;u&gt;2022.10.18 개정&lt;/u&gt;으로 &lt;u&gt;1.85 [m] 이하&lt;/u&gt;가 되었고, 선박·항공기 등 규격이 큰 구조물을 제작할 때에는 안전성 검토를 거쳐 &lt;u&gt;2.7 [m] 이하&lt;/u&gt;까지 넓힐 수 있다.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -14742,17 +14742,17 @@
       </c>
       <c r="AG106" s="32" t="inlineStr">
         <is>
-          <t>끊어진 소선의 수가 &lt;strong&gt;10% 이상&lt;/strong&gt; 이라야 사용금지다. &lt;strong&gt;「7%」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용금지 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10% 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「7%」가 아니다&lt;/u&gt; — 필러선은 세지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7%를 넘는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열이나 전기불꽃에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>끊어진 소선의 수가 &lt;strong&gt;10% 이상&lt;/strong&gt;이라야 사용금지다. &lt;strong&gt;「7%」가 아니다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;와이어로프의 사용금지 기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;이음매가 있는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;한 꼬임에서 끊어진 소선의 수가 10% 이상인 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;「7%」가 아니다&lt;/u&gt; — 필러선은 세지 않는다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지름의 감소가 공칭지름의 7%를 넘는 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;꼬인 것 · 심하게 변형되거나 부식된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;열이나 전기불꽃에 의해 손상된 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH106" s="32" t="inlineStr">
         <is>
-          <t>① 이음매가 있는 것은 사용금지 기준이다.&lt;br&gt;③ 지름 감소가 공칭지름의 7% 를 넘는 것도 그렇다.&lt;br&gt;④ 심하게 변형되거나 부식된 것도 그렇다.</t>
+          <t>① 이음매가 있는 것은 사용금지 기준이다.&lt;br&gt;③ 지름 감소가 공칭지름의 7%를 넘는 것도 그렇다.&lt;br&gt;④ 심하게 변형되거나 부식된 것도 그렇다.</t>
         </is>
       </c>
       <c r="AI106" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;와이어로프의 사용금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「소선 10% · 지름 7%」&lt;/strong&gt; 두 숫자가 짝인데 &lt;strong&gt;문항이 앞의 것을 7 로 바꿔&lt;/strong&gt; 놓았다. &lt;strong&gt;끊어진 가닥은 10%, 가늘어진 정도는 7%&lt;/strong&gt;로 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10%, 지름 7%&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;와이어로프의 사용금지&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「소선 10% · 지름 7%」&lt;/strong&gt; 두 숫자가 짝인데 &lt;strong&gt;문항이 앞의 것을 7로 바꿔&lt;/strong&gt; 놓았다. &lt;strong&gt;끊어진 가닥은 10%, 가늘어진 정도는 7%&lt;/strong&gt;로 갈라 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;소선 10%, 지름 7%&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15645,17 +15645,17 @@
       </c>
       <c r="AG113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;1.8 [m] 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;잠함·우물통 내부 굴착작업&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바닥에서 천장 또는 보까지의 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 [m] 이상&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;침하관계도에 따른 굴착방법과 재하량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해 두고 지킬 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깊이 20 [m] 를 넘으면 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 미만이면 작업 중지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착 깊이가 20 [m] 를 넘으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;송기설비 · 통신설비 · 비상용 사다리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;1.8 [m] 이상&lt;/strong&gt;이다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;잠함·우물통 내부 굴착작업&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;바닥에서 천장 또는 보까지의 높이&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.8 [m] 이상&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;침하관계도에 따른 굴착방법과 재하량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;정해 두고 지킬 것&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;승강설비&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;깊이 20 [m]를 넘으면 설치&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;산소 농도&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;18% 미만이면 작업 중지&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;굴착 깊이가 20 [m]를 넘으면&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;송기설비 · 통신설비 · 비상용 사다리&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH113" s="32" t="inlineStr">
         <is>
-          <t>② 2 [m] 는 기준값이 아니다.&lt;br&gt;③ 2.5 [m] 도 그렇다.&lt;br&gt;④ 3 [m] 도 그렇다.</t>
+          <t>② 2 [m]는 기준값이 아니다.&lt;br&gt;③ 2.5 [m] 도 그렇다.&lt;br&gt;④ 3 [m] 도 그렇다.</t>
         </is>
       </c>
       <c r="AI113" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;잠함 내 굴착작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m] 는 사람이 서서 일하고 급히 몸을 피할 수 있는 높이&lt;/strong&gt;다 — &lt;strong&gt;「20 [m] 초과 시 승강설비 · 송기설비」&lt;/strong&gt;라는 숫자와 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;천장까지 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;잠함 내 굴착작업&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;1.8 [m]는 사람이 서서 일하고 급히 몸을 피할 수 있는 높이&lt;/strong&gt;다 — &lt;strong&gt;「20 [m] 초과 시 승강설비 · 송기설비」&lt;/strong&gt;라는 숫자와 함께 잡아 둔다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;천장까지 1.8 [m] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -15903,7 +15903,7 @@
       </c>
       <c r="AG115" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;발끝막이판(폭목)&lt;/strong&gt;은 &lt;strong&gt;공구나 자재가 발판 밖으로 굴러떨어지지 않게&lt;/strong&gt; 막는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm] 를 넘으면 중간 난간대를 60 [cm] 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 바닥의 중간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판(폭목)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물체가 떨어지지 않게&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대를 지지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 방향으로 100 [kg] 이상에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;발끝막이판(폭목)&lt;/strong&gt;은 &lt;strong&gt;공구나 자재가 발판 밖으로 굴러떨어지지 않게&lt;/strong&gt; 막는다.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;안전난간의 구성&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;부재&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;상부 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 90 [cm] 이상 120 [cm] 이하&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;120 [cm]를 넘으면 중간 난간대를 60 [cm] 이내마다&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;중간 난간대&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;상부 난간대와 바닥의 중간&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;발끝막이판(폭목)&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;바닥에서 10 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;물체가 떨어지지 않게&lt;/u&gt; · 이 문항&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;난간기둥&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;난간대를 지지&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;하중&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;임의의 방향으로 100 [kg] 이상에 견딜 것&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH115" s="32" t="inlineStr">
@@ -16032,17 +16032,17 @@
       </c>
       <c r="AG116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;강우량 시간당 1 [mm] 이상&lt;/strong&gt;이면 멈춘다. &lt;strong&gt;1.5 [mm/hr] 는 그 기준을 넘는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이 문항의 보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m/s] 는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [mm/hr] 는 초과&lt;/u&gt; · 정답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [mm/hr] = 0.5 [cm] 로 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지진&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
+          <t>&lt;strong&gt;강우량 시간당 1 [mm] 이상&lt;/strong&gt;이면 멈춘다. &lt;strong&gt;1.5 [mm/hr]는 그 기준을 넘는다&lt;/strong&gt;.&lt;div style="margin:12px 0 2px;font-weight:700"&gt;철골작업의 중지기준&lt;/div&gt;&lt;div style="overflow-x:auto"&gt;&lt;table style="border-collapse:collapse;margin:10px auto;font-size:.96em"&gt;&lt;thead&gt;&lt;tr&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;항목&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;기준&lt;/th&gt;&lt;th style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;background:#f1f5f9;font-weight:700;"&gt;이 문항의 보기&lt;/th&gt;&lt;/tr&gt;&lt;/thead&gt;&lt;tbody&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;풍속&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;초당 10 [m] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;8 [m/s]는 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강우량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [mm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;1.5 [mm/hr]는 초과&lt;/u&gt; · 정답&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;강설량&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;시간당 1 [cm] 이상&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;5 [mm/hr] = 0.5 [cm]로 미달&lt;/u&gt;&lt;/td&gt;&lt;/tr&gt;&lt;tr&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:center;"&gt;&lt;u&gt;지진&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;u&gt;중지기준에 없다&lt;/u&gt;&lt;/td&gt;&lt;td style="border:1px solid #cbd5e1;padding:7px 12px;vertical-align:middle;text-align:left;"&gt;&lt;/td&gt;&lt;/tr&gt;&lt;/tbody&gt;&lt;/table&gt;&lt;/div&gt;</t>
         </is>
       </c>
       <c r="AH116" s="32" t="inlineStr">
         <is>
-          <t>② 풍속 8 [m/s] 는 기준 10 [m/s] 에 못 미친다.&lt;br&gt;③ 강설량 5 [mm/hr] 는 0.5 [cm] 로 기준 1 [cm] 에 못 미친다.&lt;br&gt;④ 지진 진도는 철골작업 중지기준에 들지 않는다.</t>
+          <t>② 풍속 8 [m/s]는 기준 10 [m/s]에 못 미친다.&lt;br&gt;③ 강설량 5 [mm/hr]는 0.5 [cm]로 기준 1 [cm]에 못 미친다.&lt;br&gt;④ 지진 진도는 철골작업 중지기준에 들지 않는다.</t>
         </is>
       </c>
       <c r="AI116" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;철골작업의 악천후 중지기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 [m/s] · 1 [mm/hr] · 1 [cm/hr]」&lt;/strong&gt; 셋을 놓고 보기의 값과 하나씩 견준다 — &lt;strong&gt;강설량 5 [mm] 를 [cm] 로 바꾸면 0.5&lt;/strong&gt;라 미달이다. &lt;strong&gt;단위 환산이 갈림길&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비는 1 [mm], 눈은 1 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;철골작업의 악천후 중지기준&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「10 [m/s] · 1 [mm/hr] · 1 [cm/hr]」&lt;/strong&gt; 셋을 놓고 보기의 값과 하나씩 견준다 — &lt;strong&gt;강설량 5 [mm]를 [cm]로 바꾸면 0.5&lt;/strong&gt;라 미달이다. &lt;strong&gt;단위 환산이 갈림길&lt;/strong&gt;이다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;비는 1 [mm], 눈은 1 [cm]&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16558,7 +16558,7 @@
       </c>
       <c r="AI120" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;핸드 브레이커&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「사람이 손에 쥐는」 장비만 작업시간을 제한&lt;/strong&gt; 한다 — &lt;strong&gt;진동이 손과 팔로 그대로 들어와 백랍병(레이노 현상)을 일으키기&lt;/strong&gt; 때문이다. &lt;strong&gt;나머지 셋은 기계에 달려 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업시간 제한은 핸드 브레이커&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;핸드 브레이커&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;「사람이 손에 쥐는」 장비만 작업시간을 제한&lt;/strong&gt;한다 — &lt;strong&gt;진동이 손과 팔로 그대로 들어와 백랍병(레이노 현상)을 일으키기&lt;/strong&gt; 때문이다. &lt;strong&gt;나머지 셋은 기계에 달려 있다&lt;/strong&gt;.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;작업시간 제한은 핸드 브레이커&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
@@ -16687,7 +16687,7 @@
       </c>
       <c r="AI121" s="32" t="inlineStr">
         <is>
-          <t>&lt;strong&gt;화물취급작업의 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [cm] 는 사람이 짐을 들고 지나갈 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;부두는 한쪽이 바다라 좁으면 그대로 빠진다&lt;/strong&gt;. &lt;strong&gt;작업발판 40 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두 통로는 폭 90 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
+          <t>&lt;strong&gt;화물취급작업의 안전조치&lt;/strong&gt;&lt;br&gt;&lt;strong&gt;90 [cm]는 사람이 짐을 들고 지나갈 수 있는 폭&lt;/strong&gt;이다 — &lt;strong&gt;부두는 한쪽이 바다라 좁으면 그대로 빠진다&lt;/strong&gt;. &lt;strong&gt;작업발판 40 [cm] 와는 다른 자리&lt;/strong&gt;다.&lt;p&gt;&lt;strong&gt;◈ 암기&lt;/strong&gt; &lt;u&gt;부두 통로는 폭 90 [cm] 이상&lt;/u&gt;.&lt;/p&gt;</t>
         </is>
       </c>
     </row>
